--- a/output/Data and Chart Outputs/egypt_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/egypt_gas_monthly.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Implied net LNG" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - CAPMAS energy balance" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Gas for power FY" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly - JODI (fallback)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JODI (fallback) raw" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly JODI (fallback)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JODI (fallback) all rows" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual official" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks FY" sheetId="12" state="visible" r:id="rId12"/>
@@ -1940,14 +1940,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>'Monthly - JODI (fallback)': the balance used by the charts (JODI fallback rows in mcm and Bcf/d, implied net LNG).</t>
+          <t>'Monthly JODI (fallback)': the balance used by the charts (JODI fallback rows in mcm and Bcf/d, implied net LNG).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>'JODI (fallback) raw': every JODI Egypt balance row in mcm, incl. the reported LNG rows (reference only).</t>
+          <t>'JODI (fallback) all rows': every JODI Egypt balance row in mcm, incl. the reported LNG rows (reference only).</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Last run 2026-10-12 01:16 UTC.</t>
+          <t>Last run 2026-10-12 01:19 UTC.</t>
         </is>
       </c>
     </row>
@@ -42271,13 +42271,13 @@
         <v>52241</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="S5" t="n">
         <v>50501</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.951</v>
       </c>
       <c r="U5" t="n">
         <v>514</v>
@@ -42289,7 +42289,7 @@
         <v>2254</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2</v>
+        <v>0.161</v>
       </c>
       <c r="Y5" t="n">
         <v>21553</v>
@@ -42348,19 +42348,19 @@
         <v>46788</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9</v>
+        <v>0.947</v>
       </c>
       <c r="S6" t="n">
         <v>47488</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>1.006</v>
       </c>
       <c r="U6" t="n">
         <v>1053</v>
       </c>
       <c r="V6" t="n">
-        <v>3.3</v>
+        <v>3.316</v>
       </c>
       <c r="W6" t="n">
         <v>353</v>
@@ -42425,19 +42425,19 @@
         <v>168</v>
       </c>
       <c r="R7" t="n">
-        <v>250.6</v>
+        <v>250.611</v>
       </c>
       <c r="S7" t="n">
         <v>168</v>
       </c>
       <c r="T7" t="n">
-        <v>305.2</v>
+        <v>305.235</v>
       </c>
       <c r="U7" t="n">
         <v>7576</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Y7" t="n">
         <v>17633</v>
@@ -42496,25 +42496,25 @@
         <v>46262</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1</v>
+        <v>1.096</v>
       </c>
       <c r="S8" t="n">
         <v>55150</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1</v>
+        <v>1.055</v>
       </c>
       <c r="U8" t="n">
         <v>10386</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9</v>
+        <v>0.858</v>
       </c>
       <c r="W8" t="n">
         <v>1498</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9</v>
+        <v>0.888</v>
       </c>
       <c r="Y8" t="n">
         <v>20615</v>
@@ -42623,13 +42623,13 @@
         <v>66060</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>1.021</v>
       </c>
       <c r="S10" t="n">
         <v>61628</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="U10" t="n">
         <v>1461</v>
@@ -42641,7 +42641,7 @@
         <v>5893</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="Y10" t="n">
         <v>22275</v>
@@ -42750,19 +42750,19 @@
         <v>57241</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.231</v>
       </c>
       <c r="U12" t="n">
         <v>3085</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.367</v>
       </c>
       <c r="W12" t="n">
         <v>6695</v>
       </c>
       <c r="X12" t="n">
-        <v>1.6</v>
+        <v>1.572</v>
       </c>
       <c r="Y12" t="n">
         <v>10754</v>
@@ -42821,19 +42821,19 @@
         <v>59322</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1</v>
+        <v>1.129</v>
       </c>
       <c r="U13" t="n">
         <v>4494</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.395</v>
       </c>
       <c r="W13" t="n">
         <v>9631</v>
       </c>
       <c r="X13" t="n">
-        <v>1.3</v>
+        <v>1.251</v>
       </c>
       <c r="Y13" t="n">
         <v>12415</v>
@@ -43619,12 +43619,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-12 01:16 UTC</t>
+          <t>2026-10-12 01:19 UTC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-12 01:16 UTC</t>
+          <t>2026-10-12 01:19 UTC</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-12 01:16 UTC</t>
+          <t>2026-10-12 01:19 UTC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -43679,7 +43679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-12 01:16 UTC</t>
+          <t>2026-10-12 01:19 UTC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/output/Data and Chart Outputs/egypt_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/egypt_gas_monthly.xlsx
@@ -2012,7 +2012,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Last run 2026-10-12 01:19 UTC.</t>
+          <t>Last run 2026-10-12 01:21 UTC.</t>
         </is>
       </c>
     </row>
@@ -43614,21 +43614,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Egypt country handle 28, TIME handles 24-210</t>
+          <t>Egypt country handle 28, TIME handles 198-210</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-12 01:19 UTC</t>
+          <t>2026-10-12 01:21 UTC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-12 01:19 UTC</t>
+          <t>2026-10-12 01:21 UTC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2385</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-12 01:19 UTC</t>
+          <t>2026-10-12 01:21 UTC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -43679,7 +43679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-12 01:19 UTC</t>
+          <t>2026-10-12 01:21 UTC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/output/Data and Chart Outputs/egypt_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/egypt_gas_monthly.xlsx
@@ -168,7 +168,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Egypt gas balance (JODI fallback; LNG implied from the balance) (to Jul/26)</a:t>
+              <a:t>Egypt gas balance (JODI fallback; LNG implied from the balance) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -198,12 +198,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$188</f>
+              <f>'Chart'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$188</f>
+              <f>'Chart'!$B$2:$B$189</f>
             </numRef>
           </val>
         </ser>
@@ -226,12 +226,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$188</f>
+              <f>'Chart'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$188</f>
+              <f>'Chart'!$C$2:$C$189</f>
             </numRef>
           </val>
         </ser>
@@ -254,12 +254,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$188</f>
+              <f>'Chart'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$188</f>
+              <f>'Chart'!$D$2:$D$189</f>
             </numRef>
           </val>
         </ser>
@@ -296,12 +296,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$188</f>
+              <f>'Chart'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$188</f>
+              <f>'Chart'!$E$2:$E$189</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -401,7 +401,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Egypt gas production (JODI fallback) (to Jul/26)</a:t>
+              <a:t>Egypt gas production (JODI fallback) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -437,12 +437,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Production'!$A$2:$A$188</f>
+              <f>'Chart - Production'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Production'!$B$2:$B$188</f>
+              <f>'Chart - Production'!$B$2:$B$189</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -538,7 +538,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Egypt gas for power vs total gas consumption (JODI fallback) (to Jul/26)</a:t>
+              <a:t>Egypt gas for power vs total gas consumption (JODI fallback) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -574,12 +574,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Power vs consumption'!$A$2:$A$188</f>
+              <f>'Chart - Power vs consumption'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Power vs consumption'!$B$2:$B$188</f>
+              <f>'Chart - Power vs consumption'!$B$2:$B$189</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -610,12 +610,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Power vs consumption'!$A$2:$A$188</f>
+              <f>'Chart - Power vs consumption'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Power vs consumption'!$C$2:$C$188</f>
+              <f>'Chart - Power vs consumption'!$C$2:$C$189</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -715,7 +715,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Egypt implied net LNG imports (+) / exports (-) (JODI fallback balance) (to Jul/26)</a:t>
+              <a:t>Egypt implied net LNG imports (+) / exports (-) (JODI fallback balance) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -745,12 +745,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Implied net LNG'!$A$2:$A$188</f>
+              <f>'Chart - Implied net LNG'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Implied net LNG'!$B$2:$B$188</f>
+              <f>'Chart - Implied net LNG'!$B$2:$B$189</f>
             </numRef>
           </val>
         </ser>
@@ -773,12 +773,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Implied net LNG'!$A$2:$A$188</f>
+              <f>'Chart - Implied net LNG'!$A$2:$A$189</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Implied net LNG'!$C$2:$C$188</f>
+              <f>'Chart - Implied net LNG'!$C$2:$C$189</f>
             </numRef>
           </val>
         </ser>
@@ -1983,7 +1983,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JODI Egypt from Jan 2011; latest month with production: Jul 2026</t>
+          <t>JODI Egypt from Jan 2011; latest month with production: Aug 2026</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Last run 2026-10-12 01:21 UTC.</t>
+          <t>Last run 2026-10-28 01:08 UTC.</t>
         </is>
       </c>
     </row>
@@ -42988,46 +42988,46 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>22685.9</v>
+        <v>25875.2</v>
       </c>
       <c r="D17" t="n">
-        <v>5332.2</v>
+        <v>6383.2</v>
       </c>
       <c r="E17" t="n">
-        <v>177.9</v>
+        <v>208.6</v>
       </c>
       <c r="F17" t="n">
-        <v>38800.5</v>
+        <v>44996.3</v>
       </c>
       <c r="G17" t="n">
-        <v>38578.4</v>
+        <v>44751.3</v>
       </c>
       <c r="H17" t="n">
-        <v>21921.9</v>
+        <v>25875.7</v>
       </c>
       <c r="I17" t="n">
-        <v>11098</v>
+        <v>13067</v>
       </c>
       <c r="J17" t="n">
         <v>318</v>
       </c>
       <c r="K17" t="n">
-        <v>16431.1</v>
+        <v>19451.1</v>
       </c>
       <c r="L17" t="n">
-        <v>496.5</v>
+        <v>527.2</v>
       </c>
       <c r="N17" t="n">
-        <v>10780</v>
+        <v>12749</v>
       </c>
       <c r="O17" t="n">
-        <v>10960.3</v>
+        <v>12946.5</v>
       </c>
       <c r="P17" t="n">
-        <v>180.3</v>
+        <v>197.5</v>
       </c>
     </row>
   </sheetData>
@@ -43557,7 +43557,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -43614,21 +43614,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Egypt country handle 28, TIME handles 198-210</t>
+          <t>Egypt country handle 28, TIME handles 198-212</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-12 01:21 UTC</t>
+          <t>2026-10-28 01:08 UTC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-12 01:21 UTC</t>
+          <t>2026-10-28 01:08 UTC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-12 01:21 UTC</t>
+          <t>2026-10-28 01:08 UTC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -43679,7 +43679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-12 01:21 UTC</t>
+          <t>2026-10-28 01:08 UTC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -43702,7 +43702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46912,6 +46912,23 @@
       </c>
       <c r="E188" t="n">
         <v>7.3906</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3.6333</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.1973</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2.2626</v>
+      </c>
+      <c r="E189" t="n">
+        <v>7.0932</v>
       </c>
     </row>
   </sheetData>
@@ -46926,7 +46943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -48438,6 +48455,14 @@
       </c>
       <c r="B188" t="n">
         <v>3.6412</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3.6333</v>
       </c>
     </row>
   </sheetData>
@@ -48452,7 +48477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -50530,6 +50555,17 @@
       </c>
       <c r="C188" t="n">
         <v>4.6794</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B189" t="n">
+        <v>7.0582</v>
+      </c>
+      <c r="C189" t="n">
+        <v>4.5041</v>
       </c>
     </row>
   </sheetData>
@@ -50544,7 +50580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -52621,6 +52657,17 @@
         <v>2.6069</v>
       </c>
       <c r="C188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2.2626</v>
+      </c>
+      <c r="C189" t="n">
         <v>0</v>
       </c>
     </row>
@@ -53104,7 +53151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S188"/>
+  <dimension ref="A1:S189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63965,6 +64012,59 @@
       </c>
       <c r="S188" t="n">
         <v>2.6069</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3189.35</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D189" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6195.83</v>
+      </c>
+      <c r="F189" t="n">
+        <v>6172.96</v>
+      </c>
+      <c r="G189" t="n">
+        <v>3953.79</v>
+      </c>
+      <c r="I189" t="n">
+        <v>6226.53</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1986.18</v>
+      </c>
+      <c r="K189" t="n">
+        <v>3.6333</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1.1973</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N189" t="n">
+        <v>7.0582</v>
+      </c>
+      <c r="O189" t="n">
+        <v>7.0321</v>
+      </c>
+      <c r="P189" t="n">
+        <v>4.5041</v>
+      </c>
+      <c r="R189" t="n">
+        <v>7.0932</v>
+      </c>
+      <c r="S189" t="n">
+        <v>2.2626</v>
       </c>
     </row>
   </sheetData>
@@ -63978,7 +64078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:O189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72148,6 +72248,47 @@
         <v>4107.7</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3189.35</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>3020</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1969</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1051</v>
+      </c>
+      <c r="G189" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="K189" t="n">
+        <v>6172.96</v>
+      </c>
+      <c r="L189" t="n">
+        <v>-22.87</v>
+      </c>
+      <c r="M189" t="n">
+        <v>6195.83</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3953.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
